--- a/docs/downloads/20260813_Johor_Teduh_Weekly_Update.xlsx
+++ b/docs/downloads/20260813_Johor_Teduh_Weekly_Update.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AC20"/>
+  <dimension ref="A2:AF20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -522,7 +522,10 @@
     <col width="9" customWidth="1" min="26" max="26"/>
     <col width="9" customWidth="1" min="27" max="27"/>
     <col width="9" customWidth="1" min="28" max="28"/>
-    <col width="46" customWidth="1" min="29" max="29"/>
+    <col width="9" customWidth="1" min="29" max="29"/>
+    <col width="9" customWidth="1" min="30" max="30"/>
+    <col width="9" customWidth="1" min="31" max="31"/>
+    <col width="46" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -559,8 +562,11 @@
       <c r="W3" s="3" t="n">
         <v>46234</v>
       </c>
-      <c r="Z3" s="4" t="n">
+      <c r="Z3" s="3" t="n">
         <v>46241</v>
+      </c>
+      <c r="AC3" s="4" t="n">
+        <v>46248</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -690,22 +696,37 @@
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="Z4" s="6" t="inlineStr">
+      <c r="Z4" s="5" t="inlineStr">
         <is>
           <t>NEW SALES</t>
         </is>
       </c>
-      <c r="AA4" s="6" t="inlineStr">
+      <c r="AA4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="AB4" s="6" t="inlineStr">
+      <c r="AB4" s="5" t="inlineStr">
         <is>
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="AC4" s="5" t="inlineStr">
+      <c r="AC4" s="6" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="AD4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="AE4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL %</t>
+        </is>
+      </c>
+      <c r="AF4" s="5" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
@@ -745,6 +766,9 @@
       <c r="AA5" s="8" t="n"/>
       <c r="AB5" s="8" t="n"/>
       <c r="AC5" s="8" t="n"/>
+      <c r="AD5" s="8" t="n"/>
+      <c r="AE5" s="8" t="n"/>
+      <c r="AF5" s="8" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
@@ -837,20 +861,31 @@
         <f>X6/$D$6</f>
         <v/>
       </c>
-      <c r="Z6" s="13">
+      <c r="Z6" s="11">
         <f>AA6-X6</f>
         <v/>
       </c>
-      <c r="AA6" s="13" t="n">
+      <c r="AA6" s="11" t="n">
         <v>293</v>
       </c>
-      <c r="AB6" s="14">
+      <c r="AB6" s="12">
         <f>AA6/$D$6</f>
         <v/>
       </c>
-      <c r="AC6" s="10" t="inlineStr">
-        <is>
-          <t>Latets sales - Block A: 187 units, Block B: 106 units</t>
+      <c r="AC6" s="13">
+        <f>AD6-AA6</f>
+        <v/>
+      </c>
+      <c r="AD6" s="13" t="n">
+        <v>297</v>
+      </c>
+      <c r="AE6" s="14">
+        <f>AD6/$D$6</f>
+        <v/>
+      </c>
+      <c r="AF6" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 188, Block B: 109</t>
         </is>
       </c>
     </row>
@@ -945,20 +980,31 @@
         <f>X7/$D$7</f>
         <v/>
       </c>
-      <c r="Z7" s="13">
+      <c r="Z7" s="11">
         <f>AA7-X7</f>
         <v/>
       </c>
-      <c r="AA7" s="13" t="n">
+      <c r="AA7" s="11" t="n">
         <v>935</v>
       </c>
-      <c r="AB7" s="14">
+      <c r="AB7" s="12">
         <f>AA7/$D$7</f>
         <v/>
       </c>
-      <c r="AC7" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 379 units, Block B: 363 units, Blok C: 86 units,  Block D: 107 units</t>
+      <c r="AC7" s="13">
+        <f>AD7-AA7</f>
+        <v/>
+      </c>
+      <c r="AD7" s="13" t="n">
+        <v>942</v>
+      </c>
+      <c r="AE7" s="14">
+        <f>AD7/$D$7</f>
+        <v/>
+      </c>
+      <c r="AF7" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 382, Block B: 367, Block C: 86, Block D: 107</t>
         </is>
       </c>
     </row>
@@ -1053,20 +1099,31 @@
         <f>X8/$D$8</f>
         <v/>
       </c>
-      <c r="Z8" s="13">
+      <c r="Z8" s="11">
         <f>AA8-X8</f>
         <v/>
       </c>
-      <c r="AA8" s="13" t="n">
+      <c r="AA8" s="11" t="n">
         <v>47</v>
       </c>
-      <c r="AB8" s="14">
+      <c r="AB8" s="12">
         <f>AA8/$D$8</f>
         <v/>
       </c>
-      <c r="AC8" s="10" t="inlineStr">
-        <is>
-          <t>Open Sale for Block A (416 units) only.</t>
+      <c r="AC8" s="13">
+        <f>AD8-AA8</f>
+        <v/>
+      </c>
+      <c r="AD8" s="13" t="n">
+        <v>47</v>
+      </c>
+      <c r="AE8" s="14">
+        <f>AD8/$D$8</f>
+        <v/>
+      </c>
+      <c r="AF8" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 47</t>
         </is>
       </c>
     </row>
@@ -1161,20 +1218,31 @@
         <f>X9/$D$9</f>
         <v/>
       </c>
-      <c r="Z9" s="13">
+      <c r="Z9" s="11">
         <f>AA9-X9</f>
         <v/>
       </c>
-      <c r="AA9" s="13" t="n">
+      <c r="AA9" s="11" t="n">
         <v>1051</v>
       </c>
-      <c r="AB9" s="14">
+      <c r="AB9" s="12">
         <f>AA9/$D$9</f>
         <v/>
       </c>
-      <c r="AC9" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Phase 1: 666 units, Phase 2: 385 units</t>
+      <c r="AC9" s="13">
+        <f>AD9-AA9</f>
+        <v/>
+      </c>
+      <c r="AD9" s="13" t="n">
+        <v>1052</v>
+      </c>
+      <c r="AE9" s="14">
+        <f>AD9/$D$9</f>
+        <v/>
+      </c>
+      <c r="AF9" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block 1A: 326, Block 1B: 340, Block 2A: 212, Block 2B: 174</t>
         </is>
       </c>
     </row>
@@ -1212,6 +1280,9 @@
       <c r="AA10" s="8" t="n"/>
       <c r="AB10" s="8" t="n"/>
       <c r="AC10" s="8" t="n"/>
+      <c r="AD10" s="8" t="n"/>
+      <c r="AE10" s="8" t="n"/>
+      <c r="AF10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
@@ -1304,18 +1375,29 @@
         <f>X11/$D$11</f>
         <v/>
       </c>
-      <c r="Z11" s="13">
+      <c r="Z11" s="11">
         <f>AA11-X11</f>
         <v/>
       </c>
-      <c r="AA11" s="13" t="n">
+      <c r="AA11" s="11" t="n">
         <v>845</v>
       </c>
-      <c r="AB11" s="14">
+      <c r="AB11" s="12">
         <f>AA11/$D$11</f>
         <v/>
       </c>
-      <c r="AC11" s="10" t="inlineStr">
+      <c r="AC11" s="13">
+        <f>AD11-AA11</f>
+        <v/>
+      </c>
+      <c r="AD11" s="13" t="n">
+        <v>845</v>
+      </c>
+      <c r="AE11" s="14">
+        <f>AD11/$D$11</f>
+        <v/>
+      </c>
+      <c r="AF11" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1412,20 +1494,31 @@
         <f>X12/$D$12</f>
         <v/>
       </c>
-      <c r="Z12" s="13">
+      <c r="Z12" s="11">
         <f>AA12-X12</f>
         <v/>
       </c>
-      <c r="AA12" s="13" t="n">
+      <c r="AA12" s="11" t="n">
         <v>1406</v>
       </c>
-      <c r="AB12" s="14">
+      <c r="AB12" s="12">
         <f>AA12/$D$12</f>
         <v/>
       </c>
-      <c r="AC12" s="10" t="inlineStr">
-        <is>
-          <t>Open sale for Block A, B &amp; D only. Block C (833 units) is not opened yet. Latest Sales - Block A: 439 units, Block B: 513 units, Block D: 454 units</t>
+      <c r="AC12" s="13">
+        <f>AD12-AA12</f>
+        <v/>
+      </c>
+      <c r="AD12" s="13" t="n">
+        <v>1417</v>
+      </c>
+      <c r="AE12" s="14">
+        <f>AD12/$D$12</f>
+        <v/>
+      </c>
+      <c r="AF12" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 446, Block B1: 231, Block B2: 284, Block D1: 168, Block D2: 288</t>
         </is>
       </c>
     </row>
@@ -1520,20 +1613,31 @@
         <f>X13/$D$13</f>
         <v/>
       </c>
-      <c r="Z13" s="13">
+      <c r="Z13" s="11">
         <f>AA13-X13</f>
         <v/>
       </c>
-      <c r="AA13" s="13" t="n">
+      <c r="AA13" s="11" t="n">
         <v>990</v>
       </c>
-      <c r="AB13" s="14">
+      <c r="AB13" s="12">
         <f>AA13/$D$13</f>
         <v/>
       </c>
-      <c r="AC13" s="10" t="inlineStr">
-        <is>
-          <t>Latest sale - Block A: 401 units, Block B: 365 units, Block C - 224 units</t>
+      <c r="AC13" s="13">
+        <f>AD13-AA13</f>
+        <v/>
+      </c>
+      <c r="AD13" s="13" t="n">
+        <v>990</v>
+      </c>
+      <c r="AE13" s="14">
+        <f>AD13/$D$13</f>
+        <v/>
+      </c>
+      <c r="AF13" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 401, Block B: 365, Block C: 224</t>
         </is>
       </c>
     </row>
@@ -1628,20 +1732,31 @@
         <f>X14/$D$14</f>
         <v/>
       </c>
-      <c r="Z14" s="13">
+      <c r="Z14" s="11">
         <f>AA14-X14</f>
         <v/>
       </c>
-      <c r="AA14" s="13" t="n">
+      <c r="AA14" s="11" t="n">
         <v>724</v>
       </c>
-      <c r="AB14" s="14">
+      <c r="AB14" s="12">
         <f>AA14/$D$14</f>
         <v/>
       </c>
-      <c r="AC14" s="10" t="inlineStr">
-        <is>
-          <t>Latest sale - Block A: 483 units, Block B: 241 units</t>
+      <c r="AC14" s="13">
+        <f>AD14-AA14</f>
+        <v/>
+      </c>
+      <c r="AD14" s="13" t="n">
+        <v>731</v>
+      </c>
+      <c r="AE14" s="14">
+        <f>AD14/$D$14</f>
+        <v/>
+      </c>
+      <c r="AF14" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 488, Block B: 243</t>
         </is>
       </c>
     </row>
@@ -1736,20 +1851,31 @@
         <f>X15/$D$15</f>
         <v/>
       </c>
-      <c r="Z15" s="13">
+      <c r="Z15" s="11">
         <f>AA15-X15</f>
         <v/>
       </c>
-      <c r="AA15" s="13" t="n">
+      <c r="AA15" s="11" t="n">
         <v>1389</v>
       </c>
-      <c r="AB15" s="14">
+      <c r="AB15" s="12">
         <f>AA15/$D$15</f>
         <v/>
       </c>
-      <c r="AC15" s="10" t="inlineStr">
-        <is>
-          <t>Latest sale - Block A: 723 units, Block B: 666 units</t>
+      <c r="AC15" s="13">
+        <f>AD15-AA15</f>
+        <v/>
+      </c>
+      <c r="AD15" s="13" t="n">
+        <v>1391</v>
+      </c>
+      <c r="AE15" s="14">
+        <f>AD15/$D$15</f>
+        <v/>
+      </c>
+      <c r="AF15" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 725, Block B: 666</t>
         </is>
       </c>
     </row>
@@ -1844,18 +1970,29 @@
         <f>X16/$D$16</f>
         <v/>
       </c>
-      <c r="Z16" s="13">
+      <c r="Z16" s="11">
         <f>AA16-X16</f>
         <v/>
       </c>
-      <c r="AA16" s="13" t="n">
+      <c r="AA16" s="11" t="n">
         <v>898</v>
       </c>
-      <c r="AB16" s="14">
+      <c r="AB16" s="12">
         <f>AA16/$D$16</f>
         <v/>
       </c>
-      <c r="AC16" s="10" t="inlineStr">
+      <c r="AC16" s="13">
+        <f>AD16-AA16</f>
+        <v/>
+      </c>
+      <c r="AD16" s="13" t="n">
+        <v>902</v>
+      </c>
+      <c r="AE16" s="14">
+        <f>AD16/$D$16</f>
+        <v/>
+      </c>
+      <c r="AF16" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1952,18 +2089,21 @@
         <f>X17/$D$17</f>
         <v/>
       </c>
-      <c r="Z17" s="13">
+      <c r="Z17" s="11">
         <f>AA17-X17</f>
         <v/>
       </c>
-      <c r="AA17" s="13" t="n">
+      <c r="AA17" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="AB17" s="14">
+      <c r="AB17" s="12">
         <f>AA17/$D$17</f>
         <v/>
       </c>
-      <c r="AC17" s="10" t="inlineStr">
+      <c r="AC17" s="13" t="n"/>
+      <c r="AD17" s="13" t="n"/>
+      <c r="AE17" s="14" t="n"/>
+      <c r="AF17" s="10" t="inlineStr">
         <is>
           <t>*No info on Teduh, Not obtained AP.</t>
         </is>
@@ -2060,20 +2200,31 @@
         <f>X18/$D$18</f>
         <v/>
       </c>
-      <c r="Z18" s="13">
+      <c r="Z18" s="11">
         <f>AA18-X18</f>
         <v/>
       </c>
-      <c r="AA18" s="13" t="n">
+      <c r="AA18" s="11" t="n">
         <v>710</v>
       </c>
-      <c r="AB18" s="14">
+      <c r="AB18" s="12">
         <f>AA18/$D$18</f>
         <v/>
       </c>
-      <c r="AC18" s="10" t="inlineStr">
-        <is>
-          <t>Latest sale - Block A: 432 units, Block B: 278 units</t>
+      <c r="AC18" s="13">
+        <f>AD18-AA18</f>
+        <v/>
+      </c>
+      <c r="AD18" s="13" t="n">
+        <v>714</v>
+      </c>
+      <c r="AE18" s="14">
+        <f>AD18/$D$18</f>
+        <v/>
+      </c>
+      <c r="AF18" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 432, Block B: 282</t>
         </is>
       </c>
     </row>
@@ -2168,20 +2319,31 @@
         <f>X19/$D$19</f>
         <v/>
       </c>
-      <c r="Z19" s="13">
+      <c r="Z19" s="11">
         <f>AA19-X19</f>
         <v/>
       </c>
-      <c r="AA19" s="13" t="n">
+      <c r="AA19" s="11" t="n">
         <v>382</v>
       </c>
-      <c r="AB19" s="14">
+      <c r="AB19" s="12">
         <f>AA19/$D$19</f>
         <v/>
       </c>
-      <c r="AC19" s="10" t="inlineStr">
-        <is>
-          <t>Latest sale - Block A: 293 units, Block B: 89 units</t>
+      <c r="AC19" s="13">
+        <f>AD19-AA19</f>
+        <v/>
+      </c>
+      <c r="AD19" s="13" t="n">
+        <v>385</v>
+      </c>
+      <c r="AE19" s="14">
+        <f>AD19/$D$19</f>
+        <v/>
+      </c>
+      <c r="AF19" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 294, Block B: 91</t>
         </is>
       </c>
     </row>
@@ -2276,27 +2438,39 @@
         <f>X20/$D$20</f>
         <v/>
       </c>
-      <c r="Z20" s="13">
+      <c r="Z20" s="11">
         <f>AA20-X20</f>
         <v/>
       </c>
-      <c r="AA20" s="13" t="n">
+      <c r="AA20" s="11" t="n">
         <v>284</v>
       </c>
-      <c r="AB20" s="14">
+      <c r="AB20" s="12">
         <f>AA20/$D$20</f>
         <v/>
       </c>
-      <c r="AC20" s="10" t="inlineStr">
-        <is>
-          <t>Latest sale - Block A: 207 units, Block B: 77 units</t>
+      <c r="AC20" s="13">
+        <f>AD20-AA20</f>
+        <v/>
+      </c>
+      <c r="AD20" s="13" t="n">
+        <v>291</v>
+      </c>
+      <c r="AE20" s="14">
+        <f>AD20/$D$20</f>
+        <v/>
+      </c>
+      <c r="AF20" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 209, Block B: 82</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="W3:Y3"/>
     <mergeCell ref="T3:V3"/>
+    <mergeCell ref="AC3:AE3"/>
     <mergeCell ref="E3:G3"/>
     <mergeCell ref="K3:M3"/>
     <mergeCell ref="H3:J3"/>
